--- a/SGC-CKN/Excel/ceecf1e2-e3e5-4afd-b48e-c78137173d3d_Lô_CT-02_P7_D800_10-04-2026.xlsx
+++ b/SGC-CKN/Excel/ceecf1e2-e3e5-4afd-b48e-c78137173d3d_Lô_CT-02_P7_D800_10-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7</t>
+    <t>P7-113</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>21:00 09/04/2026</t>
+    <t>22:00 09/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">01:20
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>Nghỉ ca 2h</t>
@@ -129,7 +129,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:10
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -139,7 +139,7 @@
   </si>
   <si>
     <t xml:space="preserve">02:50
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -149,7 +149,7 @@
   </si>
   <si>
     <t xml:space="preserve">03:20
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -159,7 +159,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:00
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -169,7 +169,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:20
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t xml:space="preserve">04:55
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>áp chân voi</t>
@@ -192,7 +192,7 @@
   </si>
   <si>
     <t xml:space="preserve">07:31
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>10</t>
@@ -202,11 +202,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:32
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:50
-10/04/2026</t>
+09/04/2026</t>
   </si>
   <si>
     <t>7h32 máy nghỉ đổi ca đến 7h45. Máy tiếp tục khoan đến 7h50</t>
